--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487746_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487746_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>A. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7938</v>
+        <v>1.1525</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5548</v>
+        <v>1.828</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.761</v>
+        <v>-0.6755</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5677</v>
+        <v>0.8122</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3876</v>
+        <v>-0.1788</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1802</v>
+        <v>0.991</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6143</v>
+        <v>2.2878</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8836</v>
+        <v>0.4737</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7307</v>
+        <v>1.8141</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0466</v>
+        <v>-1.4756</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.496</v>
+        <v>-0.6525</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5506</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.1642</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6738</v>
+        <v>-0.212</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9107</v>
+        <v>-0.2658</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7631</v>
+        <v>0.0538</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.4477</v>
+        <v>-0.6119</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4477</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ALMENARA SANABRIAS</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4796</v>
+        <v>0.8751</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4276</v>
+        <v>2.8541</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.948</v>
+        <v>-1.979</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8122</v>
+        <v>2.5677</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1788</v>
+        <v>2.3876</v>
       </c>
       <c r="I3" t="n">
-        <v>0.991</v>
+        <v>0.1802</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2878</v>
+        <v>3.6143</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4737</v>
+        <v>2.8836</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8141</v>
+        <v>0.7307</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4756</v>
+        <v>-1.0466</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6525</v>
+        <v>-0.496</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.5506</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8849</v>
+        <v>0.7551</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6662</v>
+        <v>0.21</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2187</v>
+        <v>0.5451</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6119</v>
+        <v>-2.4477</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6119</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ MORENO</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3343</v>
+        <v>0.0081</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6068</v>
+        <v>-0.9385</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2725</v>
+        <v>0.9466</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2725</v>
+        <v>1.6135</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-1.5942</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2725</v>
+        <v>3.2077</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.6935</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-1.5365</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2725</v>
+        <v>-0.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.0577</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2725</v>
+        <v>-0.0223</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6068</v>
+        <v>0.7543</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6068</v>
+        <v>-0.12</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.8743</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.1657</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>M. RODRIGUEZ MORENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2534</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9385</v>
+        <v>0.2064</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1919</v>
+        <v>-0.2725</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6135</v>
+        <v>-0.2725</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5942</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2077</v>
+        <v>-0.2725</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6935</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5365</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08</v>
+        <v>-0.2725</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0577</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0223</v>
+        <v>-0.2725</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9996</v>
+        <v>0.2064</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.12</v>
+        <v>0.2064</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1196</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1657</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4574</v>
+        <v>-0.33</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7067</v>
+        <v>-0.6066</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2493</v>
+        <v>0.2765</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9365</v>
@@ -922,13 +922,13 @@
         <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.103</v>
+        <v>0.0244</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5886</v>
+        <v>-0.6145</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2542</v>
+        <v>-4.2383</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6656</v>
+        <v>3.6237</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3446</v>
+        <v>-1.4495</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1748</v>
+        <v>-0.5792</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8303</v>
+        <v>-0.8703</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3256</v>
+        <v>-1.9926</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1781</v>
+        <v>-0.1936</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8525</v>
+        <v>-1.799</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.019</v>
+        <v>0.5431</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0033</v>
+        <v>-0.3856</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0223</v>
+        <v>0.9287</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-1.9403</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-4.0747</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.1344</v>
+        <v>1.9403</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4724</v>
+        <v>0.4573</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3017</v>
+        <v>-0.3054</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7741</v>
+        <v>0.7627</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2239</v>
+        <v>0.3776</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2239</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8058</v>
+        <v>-0.7977</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.5386</v>
+        <v>-2.3543</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7328</v>
+        <v>1.5566</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4495</v>
+        <v>-0.3446</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5792</v>
+        <v>-1.1748</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8703</v>
+        <v>0.8303</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9926</v>
+        <v>-0.3256</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1936</v>
+        <v>-1.1781</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.799</v>
+        <v>0.8525</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5431</v>
+        <v>-0.019</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3856</v>
+        <v>0.0033</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9287</v>
+        <v>-0.0223</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9403</v>
+        <v>-4.0747</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9403</v>
+        <v>2.1344</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2661</v>
+        <v>0.2633</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6057</v>
+        <v>-0.4018</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8717</v>
+        <v>0.6651</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3776</v>
+        <v>1.2239</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3776</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7707</v>
+        <v>-1.5888</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2551</v>
+        <v>-3.155</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4844</v>
+        <v>1.5662</v>
       </c>
       <c r="G9" t="n">
         <v>-0.06660000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2362</v>
+        <v>0.4181</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3623</v>
+        <v>-0.2622</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5985</v>
+        <v>0.6803</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7862</v>
+        <v>-2.0682</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2086</v>
+        <v>-1.4088</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5777</v>
+        <v>-0.6594</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9556</v>
@@ -1234,13 +1234,13 @@
         <v>1.7463</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3336</v>
+        <v>0.0516</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.12</v>
+        <v>-0.3202</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4536</v>
+        <v>0.3718</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1653</v>
+        <v>-4.2833</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0738</v>
+        <v>-3.5733</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0915</v>
+        <v>-0.71</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6077</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7517</v>
+        <v>0.1304</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9085</v>
+        <v>-0.408</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1568</v>
+        <v>0.5384</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4477</v>
@@ -1351,7 +1351,7 @@
         <v>-11.3863</v>
       </c>
       <c r="F12" t="n">
-        <v>3.673300000000001</v>
+        <v>3.6732</v>
       </c>
       <c r="G12" t="n">
         <v>0.3604000000000002</v>
@@ -1366,10 +1366,10 @@
         <v>3.963300000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2633999999999999</v>
+        <v>-0.2634</v>
       </c>
       <c r="L12" t="n">
-        <v>4.226699999999999</v>
+        <v>4.2267</v>
       </c>
       <c r="M12" t="n">
         <v>-3.6029</v>
@@ -1396,7 +1396,7 @@
         <v>-1.688</v>
       </c>
       <c r="U12" t="n">
-        <v>4.536899999999999</v>
+        <v>4.5369</v>
       </c>
       <c r="V12" t="n">
         <v>-6.071500000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4907</v>
+        <v>3.6726</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8323</v>
+        <v>1.9324</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6584</v>
+        <v>1.7401</v>
       </c>
       <c r="G13" t="n">
         <v>2.0903</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.734</v>
+        <v>-0.5521</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7268</v>
+        <v>-0.6267</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0072</v>
+        <v>0.0746</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5754</v>
+        <v>2.8579</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9036</v>
+        <v>2.4041</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6718</v>
+        <v>0.4538</v>
       </c>
       <c r="G14" t="n">
         <v>1.6129</v>
@@ -1546,13 +1546,13 @@
         <v>2.5224</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0673</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3325</v>
+        <v>-0.832</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2652</v>
+        <v>0.0471</v>
       </c>
       <c r="V14" t="n">
         <v>1.8358</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9353</v>
+        <v>2.308</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7866</v>
+        <v>0.8867</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1488</v>
+        <v>1.4213</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5399</v>
@@ -1624,13 +1624,13 @@
         <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8367</v>
+        <v>-0.464</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4845</v>
+        <v>-0.3844</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3522</v>
+        <v>-0.0796</v>
       </c>
       <c r="V15" t="n">
         <v>2.7298</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7339</v>
+        <v>1.9247</v>
       </c>
       <c r="E16" t="n">
         <v>0.7305</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0035</v>
+        <v>1.1942</v>
       </c>
       <c r="G16" t="n">
         <v>1.2546</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4908</v>
+        <v>-0.3</v>
       </c>
       <c r="T16" t="n">
         <v>-0.4845</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0063</v>
+        <v>0.1845</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0367</v>
+        <v>0.9366</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2495</v>
+        <v>0.1494</v>
       </c>
       <c r="F17" t="n">
         <v>0.7872</v>
@@ -1780,10 +1780,10 @@
         <v>2.3284</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4969</v>
+        <v>-0.597</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6046</v>
+        <v>-0.7047</v>
       </c>
       <c r="U17" t="n">
         <v>0.1077</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6196</v>
+        <v>0.0561</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0027</v>
+        <v>-2.1028</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6222</v>
+        <v>2.1589</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5996</v>
@@ -1858,13 +1858,13 @@
         <v>2.3284</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6848</v>
+        <v>0.1214</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4229</v>
+        <v>-0.523</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1077</v>
+        <v>0.6444</v>
       </c>
       <c r="V18" t="n">
         <v>0.5642</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3824</v>
+        <v>-0.0179</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0875</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3.4699</v>
+        <v>-0.0179</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.139</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6871</v>
+        <v>0.1335</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6151</v>
+        <v>-0.2725</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3486</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9804</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6318</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2766</v>
+        <v>-0.139</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2933</v>
+        <v>0.1335</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0167</v>
+        <v>-0.2725</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1045</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3284</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5709</v>
+        <v>0.1211</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3656</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2053</v>
+        <v>0.1211</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0911</v>
+        <v>-0.1518</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-2.3652</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0911</v>
+        <v>2.2134</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.139</v>
+        <v>-0.3826</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1335</v>
+        <v>-0.4226</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2725</v>
+        <v>0.0401</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.9815</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.9104</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.0711</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.139</v>
+        <v>0.5989</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1335</v>
+        <v>0.4877</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2725</v>
+        <v>0.1112</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.5821</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3582</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2302</v>
+        <v>-0.6334</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.5897</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2302</v>
+        <v>-0.0437</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.2182</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8657</v>
+        <v>-3.6881</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9409</v>
+        <v>3.4699</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3826</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4226</v>
+        <v>-0.6871</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0401</v>
+        <v>0.6151</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9815</v>
+        <v>-0.3486</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9104</v>
+        <v>-0.9804</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0711</v>
+        <v>0.6318</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5989</v>
+        <v>0.2766</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4877</v>
+        <v>0.2933</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1112</v>
+        <v>-0.0167</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5821</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3582</v>
+        <v>-3.1045</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9403</v>
+        <v>2.3284</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4065</v>
+        <v>-0.0297</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0902</v>
+        <v>-0.235</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3163</v>
+        <v>0.2053</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2821</v>
+        <v>0.6597</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2821</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1928</v>
+        <v>-1.3836</v>
       </c>
       <c r="E22" t="n">
         <v>-0.473</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7198</v>
+        <v>-0.9106</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1621</v>
@@ -2170,13 +2170,13 @@
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3573</v>
+        <v>0.1666</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1211</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4785</v>
+        <v>0.2877</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0345</v>
+        <v>-2.2714</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7469</v>
+        <v>-1.1473</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2876</v>
+        <v>-1.1241</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5388</v>
@@ -2248,13 +2248,13 @@
         <v>1.5523</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3401</v>
+        <v>0.1032</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3645</v>
+        <v>-0.0359</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0244</v>
+        <v>0.1391</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.712900000000001</v>
+        <v>7.713000000000001</v>
       </c>
       <c r="E24" t="n">
         <v>-3.6733</v>
       </c>
       <c r="F24" t="n">
-        <v>11.3864</v>
+        <v>11.3862</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3605000000000005</v>
@@ -2311,7 +2311,7 @@
         <v>-3.9631</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2635000000000001</v>
+        <v>0.2635</v>
       </c>
       <c r="O24" t="n">
         <v>-4.2267</v>
@@ -2326,10 +2326,10 @@
         <v>19.4034</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.8489</v>
+        <v>-2.8487</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.537000000000001</v>
+        <v>-4.537</v>
       </c>
       <c r="U24" t="n">
         <v>1.6882</v>
